--- a/out/LSTM-S4_repeat_1_000006.xlsx
+++ b/out/LSTM-S4_repeat_1_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.349999978125</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.349999978125</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002798364274668274</v>
+        <v>-5.113152705365792e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3601710698962788</v>
+        <v>0.06581025827228758</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.7210241785936004</v>
+        <v>0.1317450612097988</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08317840144220787</v>
+        <v>-0.01519829364927153</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2767128320266041</v>
+        <v>0.05056083309596241</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2767128320266041</v>
+        <v>0.05056083309596241</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2764165994083446</v>
+        <v>0.05049346794002224</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.9100906693203742</v>
+        <v>0.2069603280649097</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.098410141285317</v>
+        <v>0.4648262304554276</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1741355328912629</v>
+        <v>0.03959946472118359</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.535262562889554</v>
+        <v>0.3367629381030302</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.3050151180769588</v>
+        <v>0.0693624355333953</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.971242501918693</v>
+        <v>0.4359076316691118</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1670373783407852</v>
+        <v>0.0379851555764479</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.000039235921066</v>
+        <v>0.4424561980214322</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.06898867305674568</v>
+        <v>0.01568861925315071</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.970804490450025</v>
+        <v>0.4358079836439788</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.08595396641966753</v>
+        <v>0.0195461828627473</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.073735917772135</v>
+        <v>0.4592153450370701</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.05175598125435658</v>
+        <v>0.01176817925537965</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.091234604064684</v>
+        <v>0.463193604961955</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03934756120519703</v>
+        <v>0.008945698889074837</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.118153426721388</v>
+        <v>0.4693134159177437</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01740352871993045</v>
+        <v>0.003953926535315225</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.113578011573161</v>
+        <v>0.4682690490630101</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01380915410119079</v>
+        <v>0.003137675919314173</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.123788134285914</v>
+        <v>0.470587744349756</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.006846554441192524</v>
+        <v>0.001553422204039044</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.123660851043922</v>
+        <v>0.4705549303812415</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003977695820766841</v>
+        <v>0.0008997614318907874</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.124768980425586</v>
+        <v>0.470803118930717</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001987802510756235</v>
+        <v>0.0004488353163182084</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.124761499251936</v>
+        <v>0.470797553875112</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0009781296715345421</v>
+        <v>0.0002192225566657728</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.124731577717732</v>
+        <v>0.4707868779063155</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0005657386250213679</v>
+        <v>0.0001251684583382067</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.124884871690656</v>
+        <v>0.4708178743160781</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001869494298015841</v>
+        <v>3.740743216546624e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.124689224254531</v>
+        <v>0.4707696475226011</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>9.156901933265487e-05</v>
+        <v>1.745791147271043e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.124685292811996</v>
+        <v>0.470764896024337</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.637011873227863e-05</v>
+        <v>7.230980650542531e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.124688856196136</v>
+        <v>0.4707618871525233</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.107198491659588e-05</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.124682149121834</v>
+        <v>0.4707565006683657</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>9.546003728147707e-06</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.124683067357978</v>
+        <v>0.4707531160499149</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.732487839350877e-06</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.124676065067157</v>
+        <v>0.4707474486196411</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.124672202992062</v>
+        <v>0.4707478291546989</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.124667655679876</v>
+        <v>0.4707480574757336</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.124667745624526</v>
+        <v>0.4707481474203835</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.124666887690941</v>
+        <v>0.4707472894867987</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.124667116011976</v>
+        <v>0.4707475178078334</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.124666320347765</v>
+        <v>0.4707467221436217</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.124666382617137</v>
+        <v>0.4707467844129947</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.124666410292415</v>
+        <v>0.4707468120882716</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.124666562506437</v>
+        <v>0.4707469643022949</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.124666216565476</v>
+        <v>0.4707466183613331</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.124666292672488</v>
+        <v>0.4707466944683448</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.124666458724149</v>
+        <v>0.4707468605200064</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.124666818502749</v>
+        <v>0.4707472202986064</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.124666839259207</v>
+        <v>0.4707472410550642</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.124666943041495</v>
+        <v>0.4707473448373526</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.12466717136253</v>
+        <v>0.4707475731583873</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.124667046823784</v>
+        <v>0.4707474486196411</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.124667074499061</v>
+        <v>0.470747476294918</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.124667129849615</v>
+        <v>0.470747531645472</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.124667392764745</v>
+        <v>0.4707477945606026</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.124667309738915</v>
+        <v>0.4707477115347719</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.124667102174338</v>
+        <v>0.470747503970195</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.124667116011976</v>
+        <v>0.4707475178078334</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.124667254388361</v>
+        <v>0.4707476561842181</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.124666970716772</v>
+        <v>0.4707473725126295</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.124666797746291</v>
+        <v>0.4707471995421487</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.124666693964003</v>
+        <v>0.4707470957598602</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.124666839259207</v>
+        <v>0.4707472410550642</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.12466708141788</v>
+        <v>0.4707474832137374</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.124666908447399</v>
+        <v>0.4707473102432564</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.124666610938172</v>
+        <v>0.4707470127340295</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.124666597100533</v>
+        <v>0.4707469988963909</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.124666230403114</v>
+        <v>0.4707466321989717</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.124666230403114</v>
+        <v>0.4707466321989717</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.124666168133741</v>
+        <v>0.4707465699295986</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.124666064351453</v>
+        <v>0.4707464661473101</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.124665891380972</v>
+        <v>0.4707462931768294</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.124665939812706</v>
+        <v>0.4707463416085639</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.124665580034106</v>
+        <v>0.4707459818299639</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.124665538521191</v>
+        <v>0.4707459403170485</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.124665593871745</v>
+        <v>0.4707459956676022</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.124665649222299</v>
+        <v>0.4707460510181561</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.124665690735215</v>
+        <v>0.4707460925310715</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.124665420901264</v>
+        <v>0.4707458226971214</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.124665476251818</v>
+        <v>0.4707458780476754</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.124665621547022</v>
+        <v>0.4707460233428792</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.124665586952926</v>
+        <v>0.470745988748783</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.124665573115287</v>
+        <v>0.4707459749111444</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.124665663059937</v>
+        <v>0.4707460648557947</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.124665981325622</v>
+        <v>0.4707463831214793</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.124665801436322</v>
+        <v>0.4707462032321791</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.124665842949237</v>
+        <v>0.4707462447450946</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.124665656141118</v>
+        <v>0.4707460579369753</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.12466572532931</v>
+        <v>0.4707461271251678</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.124665524683553</v>
+        <v>0.4707459264794099</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.124665566196468</v>
+        <v>0.4707459679923253</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.124665593871745</v>
+        <v>0.4707459956676022</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-S4_repeat_1_000006.xlsx
+++ b/out/LSTM-S4_repeat_1_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.566666627777779</v>
+        <v>0.5733333205555557</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.566666627777779</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002798364274668274</v>
+        <v>-0.0002423384917185176</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3601710698962788</v>
+        <v>0.3119083056395791</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.7210241785936004</v>
+        <v>0.6244073137144895</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08317840144220787</v>
+        <v>-0.07203254541982289</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2767128320266041</v>
+        <v>0.2396334217280378</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2767128320266041</v>
+        <v>0.2396334217280378</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.566666627777779</v>
+        <v>0.5733333205555557</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2764165994083446</v>
+        <v>0.2394495636680189</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.9100906693203742</v>
+        <v>0.5648517232361537</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.349999978125</v>
+        <v>0.5733333205555557</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.098410141285317</v>
+        <v>1.370277761942913</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1741355328912629</v>
+        <v>0.1080780126876588</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.09333333222222227</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.535262562889554</v>
+        <v>1.02075777353542</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.3050151180769588</v>
+        <v>0.1893086715980068</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222227</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.971242501918693</v>
+        <v>1.291350518533924</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1670373783407852</v>
+        <v>0.1036725558843853</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.000039235921066</v>
+        <v>1.309223350619794</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.06898867305674568</v>
+        <v>0.04281827539347503</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.970804490450025</v>
+        <v>1.291078664366956</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.08595396641966753</v>
+        <v>0.0533478967234457</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.073735917772135</v>
+        <v>1.354963369276185</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.05175598125435658</v>
+        <v>0.03212232490157307</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.091234604064684</v>
+        <v>1.365823920517161</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03934756120519703</v>
+        <v>0.02442070429555706</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.118153426721388</v>
+        <v>1.382531075408913</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01740352871993045</v>
+        <v>0.01080059675375681</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.113578011573161</v>
+        <v>1.379689767093468</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01380915410119079</v>
+        <v>0.008567997953249499</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.123788134285914</v>
+        <v>1.386024577762996</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.006846554441192524</v>
+        <v>0.00424751644761858</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.123660851043922</v>
+        <v>1.38594368089867</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003977695820766841</v>
+        <v>0.00246782063378511</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.124768980425586</v>
+        <v>1.386629559639087</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001987802510756235</v>
+        <v>0.001231410316892555</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.124761499251936</v>
+        <v>1.386623020224778</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0009781296715345421</v>
+        <v>0.000604425410424921</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.124731577717732</v>
+        <v>1.386602558638568</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0005657386250213679</v>
+        <v>0.0003487911944576901</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.124884871690656</v>
+        <v>1.386695858595222</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001869494298015841</v>
+        <v>0.0001132944160405111</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.124689224254531</v>
+        <v>1.386572259559556</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>9.156901933265487e-05</v>
+        <v>5.563636097631816e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.124685292811996</v>
+        <v>1.386567930514243</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.637011873227863e-05</v>
+        <v>2.680054969141058e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.124688856196136</v>
+        <v>1.386568308093285</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.107198491659588e-05</v>
+        <v>1.159126312874283e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.124682149121834</v>
+        <v>1.386562221773274</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>9.546003728147707e-06</v>
+        <v>3.727602236888622e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.124683067357978</v>
+        <v>1.386560988582122</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.732487839350877e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.124676065067157</v>
+        <v>1.386554653721574</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.124672202992062</v>
+        <v>1.38655041111142</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.124667655679876</v>
+        <v>1.386550639432455</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.124667745624526</v>
+        <v>1.386550729377105</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.124666887690941</v>
+        <v>1.38654987144352</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.124667116011976</v>
+        <v>1.386550099764555</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.124666320347765</v>
+        <v>1.386549304100343</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.124666382617137</v>
+        <v>1.386549366369716</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.124666410292415</v>
+        <v>1.386549394044994</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.124666562506437</v>
+        <v>1.386549546259016</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.124666216565476</v>
+        <v>1.386549200318055</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.124666292672488</v>
+        <v>1.386549276425066</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.124666458724149</v>
+        <v>1.386549442476728</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.124666818502749</v>
+        <v>1.386549802255328</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.124666839259207</v>
+        <v>1.386549823011786</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.124666943041495</v>
+        <v>1.386549926794074</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.12466717136253</v>
+        <v>1.386550155115109</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.124667046823784</v>
+        <v>1.386550030576363</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.124667074499061</v>
+        <v>1.38655005825164</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.124667129849615</v>
+        <v>1.386550113602194</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.124667392764745</v>
+        <v>1.386550376517324</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.124667309738915</v>
+        <v>1.386550293491494</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.124667102174338</v>
+        <v>1.386550085926916</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.124667116011976</v>
+        <v>1.386550099764555</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.124667254388361</v>
+        <v>1.38655023814094</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.124666970716772</v>
+        <v>1.386549954469351</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.124666797746291</v>
+        <v>1.38654978149887</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.124666693964003</v>
+        <v>1.386549677716582</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.124666839259207</v>
+        <v>1.386549823011786</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.12466708141788</v>
+        <v>1.386550065170459</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.124666908447399</v>
+        <v>1.386549892199978</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.124666610938172</v>
+        <v>1.386549594690751</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.124666597100533</v>
+        <v>1.386549580853113</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.124666230403114</v>
+        <v>1.386549214155693</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.124666230403114</v>
+        <v>1.386549214155693</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.124666168133741</v>
+        <v>1.38654915188632</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.124666064351453</v>
+        <v>1.386549048104031</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.124665891380972</v>
+        <v>1.386548875133551</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.124665939812706</v>
+        <v>1.386548923565285</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.124665580034106</v>
+        <v>1.386548563786685</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.124665538521191</v>
+        <v>1.38654852227377</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.124665593871745</v>
+        <v>1.386548577624324</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.124665649222299</v>
+        <v>1.386548632974878</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.124665690735215</v>
+        <v>1.386548674487793</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.124665420901264</v>
+        <v>1.386548404653843</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.124665476251818</v>
+        <v>1.386548460004397</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.124665621547022</v>
+        <v>1.386548605299601</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.124665586952926</v>
+        <v>1.386548570705505</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.124665573115287</v>
+        <v>1.386548556867866</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.124665663059937</v>
+        <v>1.386548646812516</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.124665981325622</v>
+        <v>1.386548965078201</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.124665801436322</v>
+        <v>1.386548785188901</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.124665842949237</v>
+        <v>1.386548826701816</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.124665656141118</v>
+        <v>1.386548639893697</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.12466572532931</v>
+        <v>1.386548709081889</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.124665524683553</v>
+        <v>1.386548508436132</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.124665566196468</v>
+        <v>1.386548549949047</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.124665593871745</v>
+        <v>1.386548577624324</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-S4_repeat_1_000006.xlsx
+++ b/out/LSTM-S4_repeat_1_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.003324180841445923</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.01999999999999985</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.001450082287192345</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.1200000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.0004385765641927719</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.09333333222222223</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.0002566948533058167</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.5733333205555557</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.0005291961133480072</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.439999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.0006242506206035614</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.439999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.0006230846047401428</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.439999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.0009226091206073761</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.439999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.001260055229067802</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.439999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.001354590058326721</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.439999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.001301432028412819</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.439999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.001260479912161827</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.439999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.001477528363466263</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.439999973333334</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.001709287986159325</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.239999973333334</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.001836067065596581</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.239999973333334</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.001926971599459648</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.239999973333334</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.002064386382699013</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.239999973333334</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.002291427925229073</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.239999973333334</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.002640418708324432</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.239999973333334</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.002656016498804092</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.239999973333334</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.002565622329711914</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.239999973333334</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.002342114225029945</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.239999973333334</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.00226915255188942</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.239999973333334</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.002413216978311539</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.239999973333334</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.002392139285802841</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.239999973333334</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.002624399960041046</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.239999973333334</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.00316261500120163</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.239999973333334</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.002994827926158905</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.239999973333334</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.002464121207594872</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.239999973333334</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.002216959372162819</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.239999973333334</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.001963328570127487</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.239999973333334</v>
+        <v>-0.16</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.001860475167632103</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.239999973333334</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.002005716785788536</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.239999973333334</v>
+        <v>-0.16</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.002426916733384132</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.239999973333334</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.002530595287680626</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.239999973333334</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.002512974664568901</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.239999973333334</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.002552768215537071</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.239999973333334</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.002372434362769127</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.239999973333334</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.002147717401385307</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.239999973333334</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.002165853977203369</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.239999973333334</v>
+        <v>-0.3</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.002209275960922241</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.239999973333334</v>
+        <v>-0.3</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.002184551209211349</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.239999973333334</v>
+        <v>-0.3</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.002460075542330742</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.239999973333334</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002423384917185176</v>
+        <v>-4.949273588997312e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3119083056395791</v>
+        <v>0.06370100638896117</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.002205183729529381</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.239999973333334</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.6244073137144895</v>
+        <v>0.1275225657239738</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.07203254541982289</v>
+        <v>-0.01471118069234559</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.001169735565781593</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.239999973333334</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2396334217280378</v>
+        <v>0.04894033296072576</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.0005658082664012909</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.239999973333334</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2396334217280378</v>
+        <v>0.04894033296072576</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.0003130268305540085</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.5733333205555557</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2394495636680189</v>
+        <v>0.04892383617888088</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.5648517232361537</v>
+        <v>0.05068151930629054</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-7.626973092556e-05</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.5733333205555557</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.370277761942913</v>
+        <v>0.1503881187265914</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1080780126876588</v>
+        <v>0.009697399754194497</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>7.867813110351562e-06</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.09333333222222227</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.02075777353542</v>
+        <v>0.1190271141579356</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1893086715980068</v>
+        <v>0.01698569781567292</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-1.911632716655731e-05</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.09333333222222227</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.291350518533924</v>
+        <v>0.1433062991053418</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1036725558843853</v>
+        <v>0.009300638933728105</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.0001271367073059082</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.309223350619794</v>
+        <v>0.1449083886353613</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.04281827539347503</v>
+        <v>0.003838221407424194</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.0004719570279121399</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.291078664366956</v>
+        <v>0.1432767852843935</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0533478967234457</v>
+        <v>0.00478309300995277</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.0001052673906087875</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.354963369276185</v>
+        <v>0.14900585385393</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.03212232490157307</v>
+        <v>0.002878034663099794</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.0004705581814050674</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.365823920517161</v>
+        <v>0.1499764323239622</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.02442070429555706</v>
+        <v>0.002186861229359956</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.000233333557844162</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.382531075408913</v>
+        <v>0.1514717506522001</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01080059675375681</v>
+        <v>0.0009644681599928893</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.001429257914423943</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.379689767093468</v>
+        <v>0.1512120721253608</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.008567997953249499</v>
+        <v>0.000764274603042394</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.002580165863037109</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.386024577762996</v>
+        <v>0.1517768079817337</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.00424751644761858</v>
+        <v>0.0003777264802856722</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.001745417714118958</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.38594368089867</v>
+        <v>0.1517649772639442</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.00246782063378511</v>
+        <v>0.0002160992566678451</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.001570025458931923</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.386629559639087</v>
+        <v>0.1518221581616574</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001231410316892555</v>
+        <v>0.0001055496283339226</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.00298924557864666</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.386623020224778</v>
+        <v>0.1518170205199076</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.000604425410424921</v>
+        <v>4.961831508525235e-05</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.00437319278717041</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.386602558638568</v>
+        <v>0.1518106033180275</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0003487911944576901</v>
+        <v>2.837652777902737e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.005201002582907677</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.386695858595222</v>
+        <v>0.1518148331666845</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001132944160405111</v>
+        <v>6.159850569859539e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.006416612304747105</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.386572259559556</v>
+        <v>0.1517987490134216</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>5.563636097631816e-05</v>
+        <v>-5.08417705457914e-07</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.007076655514538288</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.386567930514243</v>
+        <v>0.1517938125514071</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.680054969141058e-05</v>
+        <v>-2.553803869891494e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.007373947650194168</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.386568308093285</v>
+        <v>0.1517894114228021</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.159126312874283e-05</v>
+        <v>-2.629819553036738e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.007148268632590771</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.386562221773274</v>
+        <v>0.1517842562342293</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>3.727602236888622e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.006891878321766853</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.386560988582122</v>
+        <v>0.1517847959021295</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.007014507427811623</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.386554653721574</v>
+        <v>0.1517844637988063</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.006962683983147144</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.38655041111142</v>
+        <v>0.151784844333864</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.00732705183327198</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.386550639432455</v>
+        <v>0.1517850726548987</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.007725128903985023</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.386550729377105</v>
+        <v>0.1517851625995487</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.008342533372342587</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.38654987144352</v>
+        <v>0.1517843046659639</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.008726267144083977</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.386550099764555</v>
+        <v>0.1517845329869986</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.00893245916813612</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.386549304100343</v>
+        <v>0.1517837373227868</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.009240640327334404</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.386549366369716</v>
+        <v>0.1517837995921599</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.009216286242008209</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.386549394044994</v>
+        <v>0.1517838272674368</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.008898724801838398</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.386549546259016</v>
+        <v>0.1517839794814601</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.008828176185488701</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.386549200318055</v>
+        <v>0.1517836335404983</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.008632384240627289</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.386549276425066</v>
+        <v>0.15178370964751</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.008612034842371941</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.386549442476728</v>
+        <v>0.1517838756991716</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.008118616417050362</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.386549802255328</v>
+        <v>0.1517842354777716</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.007678240537643433</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.386549823011786</v>
+        <v>0.1517842562342293</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.007430347613990307</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.386549926794074</v>
+        <v>0.1517843600165178</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.007904819212853909</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.386550155115109</v>
+        <v>0.1517845883375525</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.008391814306378365</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.386550030576363</v>
+        <v>0.1517844637988063</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.008740895427763462</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.38655005825164</v>
+        <v>0.1517844914740832</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.00843485351651907</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.386550113602194</v>
+        <v>0.1517845468246371</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.008487666957080364</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.386550376517324</v>
+        <v>0.1517848097397678</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.008640537969768047</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.386550293491494</v>
+        <v>0.151784726713937</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.008806063793599606</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.386550085926916</v>
+        <v>0.1517845191493603</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.008982658386230469</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.386550099764555</v>
+        <v>0.1517845329869986</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.009077783674001694</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.38655023814094</v>
+        <v>0.1517846713633833</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.009141475893557072</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.386549954469351</v>
+        <v>0.1517843876917947</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.009117039851844311</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.38654978149887</v>
+        <v>0.1517842147213139</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.00876043364405632</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.386549677716582</v>
+        <v>0.1517841109390254</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.008515290915966034</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.386549823011786</v>
+        <v>0.1517842562342293</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.008439713157713413</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.16</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.386550065170459</v>
+        <v>0.1517844983929025</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.008502654731273651</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.3</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.386549892199978</v>
+        <v>0.1517843254224216</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.008600959554314613</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.386549594690751</v>
+        <v>0.1517840279131946</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.008659392595291138</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.386549580853113</v>
+        <v>0.1517840140755561</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.008661180734634399</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.386549214155693</v>
+        <v>0.1517836473781369</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.00845734216272831</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.386549214155693</v>
+        <v>0.1517836473781369</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.008171515539288521</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.38654915188632</v>
+        <v>0.1517835851087638</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.008134787902235985</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.386549048104031</v>
+        <v>0.1517834813264753</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.008007694035768509</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.386548875133551</v>
+        <v>0.1517833083559945</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.007793827913701534</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.386548923565285</v>
+        <v>0.1517833567877291</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.007614373229444027</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.386548563786685</v>
+        <v>0.151782997009129</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.007388864643871784</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.38654852227377</v>
+        <v>0.1517829554962136</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.006864242255687714</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.386548577624324</v>
+        <v>0.1517830108467673</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.006449064239859581</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.386548632974878</v>
+        <v>0.1517830661973213</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.006005176343023777</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.386548674487793</v>
+        <v>0.1517831077102367</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.005717954598367214</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.386548404653843</v>
+        <v>0.1517828378762866</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.005418066866695881</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.386548460004397</v>
+        <v>0.1517828932268405</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.005175473168492317</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.386548605299601</v>
+        <v>0.1517830385220444</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.004969735629856586</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.386548570705505</v>
+        <v>0.1517830039279482</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.004827219061553478</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.386548556867866</v>
+        <v>0.1517829900903097</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.004442872479557991</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.386548646812516</v>
+        <v>0.1517830800349598</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.003742153756320477</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.386548965078201</v>
+        <v>0.1517833983006445</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.003978140652179718</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.386548785188901</v>
+        <v>0.1517832184113443</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.004463780671358109</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.386548826701816</v>
+        <v>0.1517832599242597</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.004821578040719032</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.386548639893697</v>
+        <v>0.1517830731161404</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.005113851279020309</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.386548709081889</v>
+        <v>0.1517831423043329</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.005185807123780251</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.386548508436132</v>
+        <v>0.1517829416585751</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.005158011801540852</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.3000000000000002</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.386548549949047</v>
+        <v>0.1517829831714905</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.004893429577350616</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.4400000000000002</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.386548577624324</v>
+        <v>0.1517830108467673</v>
       </c>
     </row>
   </sheetData>
